--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xieyishan/Desktop/python/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xieyishan/Desktop/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E9C35B6-3747-1D40-9469-CF1A59A0DD49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C52391D-27F3-974B-8095-C5815AFED179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8640" yWindow="760" windowWidth="16040" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,9 +308,6 @@
     <t>月眉</t>
   </si>
   <si>
-    <t>九曲堂(高</t>
-  </si>
-  <si>
     <t>荖濃(新發大橋)</t>
   </si>
   <si>
@@ -357,6 +354,10 @@
   </si>
   <si>
     <t>新埤</t>
+  </si>
+  <si>
+    <t>九曲堂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7402,7 +7403,7 @@
         <v>42</v>
       </c>
       <c r="C290" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D290">
         <v>3075.66</v>
@@ -7425,7 +7426,7 @@
         <v>42</v>
       </c>
       <c r="C291" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D291">
         <v>3075.66</v>
@@ -7448,7 +7449,7 @@
         <v>42</v>
       </c>
       <c r="C292" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D292">
         <v>3075.66</v>
@@ -7471,7 +7472,7 @@
         <v>42</v>
       </c>
       <c r="C293" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D293">
         <v>3075.66</v>
@@ -7494,7 +7495,7 @@
         <v>42</v>
       </c>
       <c r="C294" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D294">
         <v>3075.66</v>
@@ -7517,7 +7518,7 @@
         <v>42</v>
       </c>
       <c r="C295" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D295">
         <v>3075.66</v>
@@ -7540,7 +7541,7 @@
         <v>42</v>
       </c>
       <c r="C296" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D296">
         <v>3075.66</v>
@@ -7563,7 +7564,7 @@
         <v>42</v>
       </c>
       <c r="C297" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D297">
         <v>3075.66</v>
@@ -7586,7 +7587,7 @@
         <v>42</v>
       </c>
       <c r="C298" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D298">
         <v>3075.66</v>
@@ -7609,7 +7610,7 @@
         <v>43</v>
       </c>
       <c r="C299" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D299">
         <v>812.03</v>
@@ -7632,7 +7633,7 @@
         <v>43</v>
       </c>
       <c r="C300" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D300">
         <v>812.03</v>
@@ -7655,7 +7656,7 @@
         <v>43</v>
       </c>
       <c r="C301" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D301">
         <v>812.03</v>
@@ -7678,7 +7679,7 @@
         <v>43</v>
       </c>
       <c r="C302" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D302">
         <v>812.03</v>
@@ -7701,7 +7702,7 @@
         <v>43</v>
       </c>
       <c r="C303" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D303">
         <v>812.03</v>
@@ -7724,7 +7725,7 @@
         <v>43</v>
       </c>
       <c r="C304" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D304">
         <v>812.03</v>
@@ -7747,7 +7748,7 @@
         <v>43</v>
       </c>
       <c r="C305" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D305">
         <v>812.03</v>
@@ -7770,7 +7771,7 @@
         <v>43</v>
       </c>
       <c r="C306" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D306">
         <v>812.03</v>
@@ -7793,7 +7794,7 @@
         <v>43</v>
       </c>
       <c r="C307" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D307">
         <v>812.03</v>
@@ -7816,7 +7817,7 @@
         <v>44</v>
       </c>
       <c r="C308" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D308">
         <v>23.06</v>
@@ -7839,7 +7840,7 @@
         <v>44</v>
       </c>
       <c r="C309" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D309">
         <v>23.06</v>
@@ -7862,7 +7863,7 @@
         <v>44</v>
       </c>
       <c r="C310" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D310">
         <v>23.06</v>
@@ -7885,7 +7886,7 @@
         <v>44</v>
       </c>
       <c r="C311" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D311">
         <v>23.06</v>
@@ -7908,7 +7909,7 @@
         <v>44</v>
       </c>
       <c r="C312" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D312">
         <v>23.06</v>
@@ -7931,7 +7932,7 @@
         <v>44</v>
       </c>
       <c r="C313" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D313">
         <v>23.06</v>
@@ -7954,7 +7955,7 @@
         <v>44</v>
       </c>
       <c r="C314" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D314">
         <v>23.06</v>
@@ -7977,7 +7978,7 @@
         <v>44</v>
       </c>
       <c r="C315" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D315">
         <v>23.06</v>
@@ -8000,7 +8001,7 @@
         <v>44</v>
       </c>
       <c r="C316" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D316">
         <v>23.06</v>
@@ -8023,7 +8024,7 @@
         <v>45</v>
       </c>
       <c r="C317" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D317">
         <v>360.2</v>
@@ -8046,7 +8047,7 @@
         <v>45</v>
       </c>
       <c r="C318" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D318">
         <v>360.2</v>
@@ -8069,7 +8070,7 @@
         <v>45</v>
       </c>
       <c r="C319" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D319">
         <v>360.2</v>
@@ -8092,7 +8093,7 @@
         <v>45</v>
       </c>
       <c r="C320" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D320">
         <v>360.2</v>
@@ -8115,7 +8116,7 @@
         <v>45</v>
       </c>
       <c r="C321" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D321">
         <v>360.2</v>
@@ -8138,7 +8139,7 @@
         <v>45</v>
       </c>
       <c r="C322" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D322">
         <v>360.2</v>
@@ -8161,7 +8162,7 @@
         <v>45</v>
       </c>
       <c r="C323" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D323">
         <v>360.2</v>
@@ -8184,7 +8185,7 @@
         <v>45</v>
       </c>
       <c r="C324" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D324">
         <v>360.2</v>
@@ -8207,7 +8208,7 @@
         <v>45</v>
       </c>
       <c r="C325" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D325">
         <v>360.2</v>
@@ -8230,7 +8231,7 @@
         <v>46</v>
       </c>
       <c r="C326" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D326">
         <v>408.51</v>
@@ -8253,7 +8254,7 @@
         <v>46</v>
       </c>
       <c r="C327" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D327">
         <v>408.51</v>
@@ -8276,7 +8277,7 @@
         <v>46</v>
       </c>
       <c r="C328" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D328">
         <v>408.51</v>
@@ -8299,7 +8300,7 @@
         <v>46</v>
       </c>
       <c r="C329" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D329">
         <v>408.51</v>
@@ -8322,7 +8323,7 @@
         <v>46</v>
       </c>
       <c r="C330" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D330">
         <v>408.51</v>
@@ -8345,7 +8346,7 @@
         <v>46</v>
       </c>
       <c r="C331" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D331">
         <v>408.51</v>
@@ -8368,7 +8369,7 @@
         <v>46</v>
       </c>
       <c r="C332" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D332">
         <v>408.51</v>
@@ -8391,7 +8392,7 @@
         <v>46</v>
       </c>
       <c r="C333" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D333">
         <v>408.51</v>
@@ -8414,7 +8415,7 @@
         <v>46</v>
       </c>
       <c r="C334" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D334">
         <v>408.51</v>
@@ -8437,7 +8438,7 @@
         <v>47</v>
       </c>
       <c r="C335" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D335">
         <v>303.63</v>
@@ -8460,7 +8461,7 @@
         <v>47</v>
       </c>
       <c r="C336" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D336">
         <v>303.63</v>
@@ -8483,7 +8484,7 @@
         <v>47</v>
       </c>
       <c r="C337" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D337">
         <v>303.63</v>
@@ -8506,7 +8507,7 @@
         <v>47</v>
       </c>
       <c r="C338" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D338">
         <v>303.63</v>
@@ -8529,7 +8530,7 @@
         <v>47</v>
       </c>
       <c r="C339" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D339">
         <v>303.63</v>
@@ -8552,7 +8553,7 @@
         <v>47</v>
       </c>
       <c r="C340" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D340">
         <v>303.63</v>
@@ -8575,7 +8576,7 @@
         <v>47</v>
       </c>
       <c r="C341" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D341">
         <v>303.63</v>
@@ -8598,7 +8599,7 @@
         <v>47</v>
       </c>
       <c r="C342" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D342">
         <v>303.63</v>
@@ -8621,7 +8622,7 @@
         <v>47</v>
       </c>
       <c r="C343" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D343">
         <v>303.63</v>
@@ -8644,7 +8645,7 @@
         <v>48</v>
       </c>
       <c r="C344" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D344">
         <v>391.7</v>
@@ -8667,7 +8668,7 @@
         <v>48</v>
       </c>
       <c r="C345" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D345">
         <v>391.7</v>
@@ -8690,7 +8691,7 @@
         <v>48</v>
       </c>
       <c r="C346" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D346">
         <v>391.7</v>
@@ -8713,7 +8714,7 @@
         <v>48</v>
       </c>
       <c r="C347" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D347">
         <v>391.7</v>
@@ -8736,7 +8737,7 @@
         <v>48</v>
       </c>
       <c r="C348" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D348">
         <v>391.7</v>
@@ -8759,7 +8760,7 @@
         <v>48</v>
       </c>
       <c r="C349" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D349">
         <v>391.7</v>
@@ -8782,7 +8783,7 @@
         <v>48</v>
       </c>
       <c r="C350" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D350">
         <v>391.7</v>
@@ -8805,7 +8806,7 @@
         <v>48</v>
       </c>
       <c r="C351" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D351">
         <v>391.7</v>
@@ -8828,7 +8829,7 @@
         <v>48</v>
       </c>
       <c r="C352" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D352">
         <v>391.7</v>
@@ -8851,7 +8852,7 @@
         <v>49</v>
       </c>
       <c r="C353" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D353">
         <v>853</v>
@@ -8874,7 +8875,7 @@
         <v>49</v>
       </c>
       <c r="C354" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D354">
         <v>853</v>
@@ -8897,7 +8898,7 @@
         <v>49</v>
       </c>
       <c r="C355" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D355">
         <v>853</v>
@@ -8920,7 +8921,7 @@
         <v>49</v>
       </c>
       <c r="C356" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D356">
         <v>853</v>
@@ -8943,7 +8944,7 @@
         <v>49</v>
       </c>
       <c r="C357" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D357">
         <v>853</v>
@@ -8966,7 +8967,7 @@
         <v>49</v>
       </c>
       <c r="C358" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D358">
         <v>853</v>
@@ -8989,7 +8990,7 @@
         <v>49</v>
       </c>
       <c r="C359" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D359">
         <v>853</v>
@@ -9012,7 +9013,7 @@
         <v>49</v>
       </c>
       <c r="C360" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D360">
         <v>853</v>
@@ -9035,7 +9036,7 @@
         <v>49</v>
       </c>
       <c r="C361" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D361">
         <v>853</v>
@@ -9058,7 +9059,7 @@
         <v>50</v>
       </c>
       <c r="C362" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D362">
         <v>375.08</v>
@@ -9081,7 +9082,7 @@
         <v>50</v>
       </c>
       <c r="C363" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D363">
         <v>375.08</v>
@@ -9104,7 +9105,7 @@
         <v>50</v>
       </c>
       <c r="C364" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D364">
         <v>375.08</v>
@@ -9127,7 +9128,7 @@
         <v>50</v>
       </c>
       <c r="C365" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D365">
         <v>375.08</v>
@@ -9150,7 +9151,7 @@
         <v>50</v>
       </c>
       <c r="C366" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D366">
         <v>375.08</v>
@@ -9173,7 +9174,7 @@
         <v>50</v>
       </c>
       <c r="C367" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D367">
         <v>375.08</v>
@@ -9196,7 +9197,7 @@
         <v>50</v>
       </c>
       <c r="C368" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D368">
         <v>375.08</v>
@@ -9219,7 +9220,7 @@
         <v>50</v>
       </c>
       <c r="C369" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D369">
         <v>375.08</v>
@@ -9242,7 +9243,7 @@
         <v>50</v>
       </c>
       <c r="C370" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D370">
         <v>375.08</v>
@@ -9265,7 +9266,7 @@
         <v>51</v>
       </c>
       <c r="C371" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D371">
         <v>519.49</v>
@@ -9288,7 +9289,7 @@
         <v>51</v>
       </c>
       <c r="C372" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D372">
         <v>519.49</v>
@@ -9311,7 +9312,7 @@
         <v>51</v>
       </c>
       <c r="C373" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D373">
         <v>519.49</v>
@@ -9334,7 +9335,7 @@
         <v>51</v>
       </c>
       <c r="C374" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D374">
         <v>519.49</v>
@@ -9357,7 +9358,7 @@
         <v>51</v>
       </c>
       <c r="C375" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D375">
         <v>519.49</v>
@@ -9380,7 +9381,7 @@
         <v>51</v>
       </c>
       <c r="C376" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D376">
         <v>519.49</v>
@@ -9403,7 +9404,7 @@
         <v>51</v>
       </c>
       <c r="C377" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D377">
         <v>519.49</v>
@@ -9426,7 +9427,7 @@
         <v>51</v>
       </c>
       <c r="C378" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D378">
         <v>519.49</v>
@@ -9449,7 +9450,7 @@
         <v>51</v>
       </c>
       <c r="C379" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D379">
         <v>519.49</v>
@@ -9472,7 +9473,7 @@
         <v>52</v>
       </c>
       <c r="C380" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D380">
         <v>2894.79</v>
@@ -9495,7 +9496,7 @@
         <v>52</v>
       </c>
       <c r="C381" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D381">
         <v>2894.79</v>
@@ -9518,7 +9519,7 @@
         <v>52</v>
       </c>
       <c r="C382" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D382">
         <v>2894.79</v>
@@ -9541,7 +9542,7 @@
         <v>52</v>
       </c>
       <c r="C383" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D383">
         <v>2894.79</v>
@@ -9564,7 +9565,7 @@
         <v>52</v>
       </c>
       <c r="C384" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D384">
         <v>2894.79</v>
@@ -9587,7 +9588,7 @@
         <v>52</v>
       </c>
       <c r="C385" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D385">
         <v>2894.79</v>
@@ -9610,7 +9611,7 @@
         <v>52</v>
       </c>
       <c r="C386" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D386">
         <v>2894.79</v>
@@ -9633,7 +9634,7 @@
         <v>52</v>
       </c>
       <c r="C387" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D387">
         <v>2894.79</v>
@@ -9656,7 +9657,7 @@
         <v>52</v>
       </c>
       <c r="C388" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D388">
         <v>2894.79</v>
@@ -9679,7 +9680,7 @@
         <v>53</v>
       </c>
       <c r="C389" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D389">
         <v>403.9</v>
@@ -9702,7 +9703,7 @@
         <v>53</v>
       </c>
       <c r="C390" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D390">
         <v>403.9</v>
@@ -9725,7 +9726,7 @@
         <v>53</v>
       </c>
       <c r="C391" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D391">
         <v>403.9</v>
@@ -9748,7 +9749,7 @@
         <v>53</v>
       </c>
       <c r="C392" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D392">
         <v>403.9</v>
@@ -9771,7 +9772,7 @@
         <v>53</v>
       </c>
       <c r="C393" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D393">
         <v>403.9</v>
@@ -9794,7 +9795,7 @@
         <v>53</v>
       </c>
       <c r="C394" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D394">
         <v>403.9</v>
@@ -9817,7 +9818,7 @@
         <v>53</v>
       </c>
       <c r="C395" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D395">
         <v>403.9</v>
@@ -9840,7 +9841,7 @@
         <v>53</v>
       </c>
       <c r="C396" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D396">
         <v>403.9</v>
@@ -9863,7 +9864,7 @@
         <v>53</v>
       </c>
       <c r="C397" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D397">
         <v>403.9</v>
@@ -9886,7 +9887,7 @@
         <v>54</v>
       </c>
       <c r="C398" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D398">
         <v>354.28</v>
@@ -9909,7 +9910,7 @@
         <v>54</v>
       </c>
       <c r="C399" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D399">
         <v>354.28</v>
@@ -9932,7 +9933,7 @@
         <v>54</v>
       </c>
       <c r="C400" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D400">
         <v>354.28</v>
@@ -9955,7 +9956,7 @@
         <v>54</v>
       </c>
       <c r="C401" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D401">
         <v>354.28</v>
@@ -9978,7 +9979,7 @@
         <v>54</v>
       </c>
       <c r="C402" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D402">
         <v>354.28</v>
@@ -10001,7 +10002,7 @@
         <v>54</v>
       </c>
       <c r="C403" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D403">
         <v>354.28</v>
@@ -10024,7 +10025,7 @@
         <v>54</v>
       </c>
       <c r="C404" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D404">
         <v>354.28</v>
@@ -10047,7 +10048,7 @@
         <v>54</v>
       </c>
       <c r="C405" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D405">
         <v>354.28</v>
@@ -10070,7 +10071,7 @@
         <v>54</v>
       </c>
       <c r="C406" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D406">
         <v>354.28</v>
@@ -10093,7 +10094,7 @@
         <v>55</v>
       </c>
       <c r="C407" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D407">
         <v>519.49</v>
@@ -10116,7 +10117,7 @@
         <v>55</v>
       </c>
       <c r="C408" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D408">
         <v>519.49</v>
@@ -10139,7 +10140,7 @@
         <v>55</v>
       </c>
       <c r="C409" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D409">
         <v>519.49</v>
@@ -10162,7 +10163,7 @@
         <v>55</v>
       </c>
       <c r="C410" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D410">
         <v>519.49</v>
@@ -10185,7 +10186,7 @@
         <v>55</v>
       </c>
       <c r="C411" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D411">
         <v>519.49</v>
@@ -10208,7 +10209,7 @@
         <v>55</v>
       </c>
       <c r="C412" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D412">
         <v>519.49</v>
@@ -10231,7 +10232,7 @@
         <v>55</v>
       </c>
       <c r="C413" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D413">
         <v>519.49</v>
@@ -10254,7 +10255,7 @@
         <v>55</v>
       </c>
       <c r="C414" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D414">
         <v>519.49</v>
@@ -10277,7 +10278,7 @@
         <v>55</v>
       </c>
       <c r="C415" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D415">
         <v>519.49</v>
@@ -10300,7 +10301,7 @@
         <v>56</v>
       </c>
       <c r="C416" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D416">
         <v>175.3</v>
@@ -10323,7 +10324,7 @@
         <v>56</v>
       </c>
       <c r="C417" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D417">
         <v>175.3</v>
@@ -10346,7 +10347,7 @@
         <v>56</v>
       </c>
       <c r="C418" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D418">
         <v>175.3</v>
@@ -10369,7 +10370,7 @@
         <v>56</v>
       </c>
       <c r="C419" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D419">
         <v>175.3</v>
@@ -10392,7 +10393,7 @@
         <v>56</v>
       </c>
       <c r="C420" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D420">
         <v>175.3</v>
@@ -10415,7 +10416,7 @@
         <v>56</v>
       </c>
       <c r="C421" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D421">
         <v>175.3</v>
@@ -10438,7 +10439,7 @@
         <v>56</v>
       </c>
       <c r="C422" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D422">
         <v>175.3</v>
@@ -10461,7 +10462,7 @@
         <v>56</v>
       </c>
       <c r="C423" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D423">
         <v>175.3</v>
@@ -10484,7 +10485,7 @@
         <v>56</v>
       </c>
       <c r="C424" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D424">
         <v>175.3</v>
@@ -10507,7 +10508,7 @@
         <v>57</v>
       </c>
       <c r="C425" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D425">
         <v>321.7</v>
@@ -10530,7 +10531,7 @@
         <v>57</v>
       </c>
       <c r="C426" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D426">
         <v>321.7</v>
@@ -10553,7 +10554,7 @@
         <v>57</v>
       </c>
       <c r="C427" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D427">
         <v>321.7</v>
@@ -10576,7 +10577,7 @@
         <v>57</v>
       </c>
       <c r="C428" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D428">
         <v>321.7</v>
@@ -10599,7 +10600,7 @@
         <v>57</v>
       </c>
       <c r="C429" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D429">
         <v>321.7</v>
@@ -10622,7 +10623,7 @@
         <v>57</v>
       </c>
       <c r="C430" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D430">
         <v>321.7</v>
@@ -10645,7 +10646,7 @@
         <v>57</v>
       </c>
       <c r="C431" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D431">
         <v>321.7</v>
@@ -10668,7 +10669,7 @@
         <v>57</v>
       </c>
       <c r="C432" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D432">
         <v>321.7</v>
@@ -10691,7 +10692,7 @@
         <v>57</v>
       </c>
       <c r="C433" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D433">
         <v>321.7</v>
@@ -10714,7 +10715,7 @@
         <v>58</v>
       </c>
       <c r="C434" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D434">
         <v>309.86</v>
@@ -10737,7 +10738,7 @@
         <v>58</v>
       </c>
       <c r="C435" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D435">
         <v>309.86</v>
@@ -10760,7 +10761,7 @@
         <v>58</v>
       </c>
       <c r="C436" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D436">
         <v>309.86</v>
@@ -10783,7 +10784,7 @@
         <v>58</v>
       </c>
       <c r="C437" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D437">
         <v>309.86</v>
@@ -10806,7 +10807,7 @@
         <v>58</v>
       </c>
       <c r="C438" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D438">
         <v>309.86</v>
@@ -10829,7 +10830,7 @@
         <v>58</v>
       </c>
       <c r="C439" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D439">
         <v>309.86</v>
@@ -10852,7 +10853,7 @@
         <v>58</v>
       </c>
       <c r="C440" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D440">
         <v>309.86</v>
@@ -10875,7 +10876,7 @@
         <v>58</v>
       </c>
       <c r="C441" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D441">
         <v>309.86</v>
@@ -10898,7 +10899,7 @@
         <v>58</v>
       </c>
       <c r="C442" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D442">
         <v>309.86</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xieyishan/Desktop/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C52391D-27F3-974B-8095-C5815AFED179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E719CCB0-ADFD-864C-AEA9-B3437FBA1342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8640" yWindow="760" windowWidth="16040" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
